--- a/dados/SURVEY_STARNAV.xlsx
+++ b/dados/SURVEY_STARNAV.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_D8CADBA4B752A30CED38DB95738FA6ECA17C7238" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A733B0E8-E9E9-4941-895C-41D7998BC52E}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="11_D8CADBA4B752A30CED38DB95738FA6ECA17C7238" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E154928-6B75-415F-9F03-88B125B2272C}"/>
   <bookViews>
-    <workbookView xWindow="1776" yWindow="1776" windowWidth="17280" windowHeight="8880" tabRatio="899" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="899" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="posicoes" sheetId="1" r:id="rId1"/>
@@ -6271,7 +6271,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
         <v>46223</v>
       </c>
@@ -6300,7 +6300,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="9">
         <v>46223</v>
       </c>
@@ -6323,7 +6323,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <v>46224.236805555563</v>
       </c>
@@ -6346,7 +6346,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>46224.848611111112</v>
       </c>
@@ -6369,7 +6369,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
         <v>46225.224305555559</v>
       </c>
@@ -6392,7 +6392,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>46225.806250000001</v>
       </c>
@@ -6415,7 +6415,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>46226.334722222222</v>
       </c>
@@ -6438,7 +6438,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>46226.90625</v>
       </c>
@@ -6455,7 +6455,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>46227.259722222218</v>
       </c>
@@ -6472,7 +6472,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>46227.911111111112</v>
       </c>
@@ -6489,7 +6489,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>46228.290972222218</v>
       </c>
@@ -6506,7 +6506,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>46229.384722222218</v>
       </c>
@@ -6523,7 +6523,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>46230.350694444453</v>
       </c>
@@ -6540,7 +6540,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>46230.87222222222</v>
       </c>

--- a/dados/SURVEY_STARNAV.xlsx
+++ b/dados/SURVEY_STARNAV.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_08ED8E5674093C57BB9E1B1F4A6EE60EDB62EA09" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2B801FB-7DB6-4787-A61E-4F6C229AB063}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="11_08ED8E5674093C57BB9E1B1F4A6EE60EDB62EA09" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3267A3D3-C8D2-4ECF-943A-02E98BC16D09}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="899" firstSheet="5" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="899" firstSheet="10" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="posicoes" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
     <sheet name="STARNAV VOLANS" sheetId="18" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'STARNAV ANDROMEDA'!$A$1:$S$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'STARNAV ANDROMEDA'!$A$1:$S$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'STARNAV AQUILA'!$A$1:$S$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'STARNAV PERSEUS'!$A$1:$S$1</definedName>
   </definedNames>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="181">
   <si>
     <t>data_consulta</t>
   </si>
@@ -561,16 +561,10 @@
     <t xml:space="preserve"> 05:53:00</t>
   </si>
   <si>
-    <t>underway using engine</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 05:35:00</t>
   </si>
   <si>
     <t>Moored</t>
-  </si>
-  <si>
-    <t>under using engine</t>
   </si>
   <si>
     <t xml:space="preserve"> 05:41:00</t>
@@ -2592,6 +2586,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="17" max="17" width="21.6640625" customWidth="1"/>
+    <col min="19" max="19" width="29.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -2679,7 +2674,7 @@
         <v>0.1965277777777778</v>
       </c>
       <c r="S2" t="s">
-        <v>173</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -2705,7 +2700,7 @@
         <v>46223</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="S3" t="s">
         <v>21</v>
@@ -2914,7 +2909,7 @@
         <v>46228.263888888891</v>
       </c>
       <c r="S13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -2997,6 +2992,7 @@
   <cols>
     <col min="1" max="1" width="38.21875" customWidth="1"/>
     <col min="17" max="17" width="19.6640625" customWidth="1"/>
+    <col min="19" max="19" width="32" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -3084,7 +3080,7 @@
         <v>1.111111111111111E-2</v>
       </c>
       <c r="S2" t="s">
-        <v>173</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -3159,7 +3155,7 @@
         <v>0.24027777777777781</v>
       </c>
       <c r="S5" t="s">
-        <v>178</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
@@ -3353,7 +3349,7 @@
         <v>46230.347222222219</v>
       </c>
       <c r="S15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
@@ -3403,6 +3399,7 @@
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="25.44140625" customWidth="1"/>
     <col min="17" max="17" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -3490,7 +3487,7 @@
         <v>0.42152777777777778</v>
       </c>
       <c r="S2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -3519,7 +3516,7 @@
         <v>0.26180555555555562</v>
       </c>
       <c r="S3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -3542,7 +3539,7 @@
         <v>0.71180555555555558</v>
       </c>
       <c r="S4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -3634,7 +3631,7 @@
         <v>20</v>
       </c>
       <c r="S8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
@@ -3873,7 +3870,7 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B2" s="3">
         <v>0.39166666666666672</v>
@@ -3927,7 +3924,7 @@
         <v>0.375</v>
       </c>
       <c r="S2" t="s">
-        <v>168</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -3956,7 +3953,7 @@
         <v>0.25208333333333333</v>
       </c>
       <c r="S3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -3979,7 +3976,7 @@
         <v>0.68888888888888888</v>
       </c>
       <c r="S4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -4002,7 +3999,7 @@
         <v>0.85</v>
       </c>
       <c r="S5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
@@ -4025,7 +4022,7 @@
         <v>20</v>
       </c>
       <c r="S6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
@@ -4196,7 +4193,7 @@
         <v>46230.331250000003</v>
       </c>
       <c r="S15" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
@@ -4248,6 +4245,7 @@
     <col min="1" max="1" width="10.88671875" customWidth="1"/>
     <col min="14" max="14" width="12.5546875" customWidth="1"/>
     <col min="17" max="17" width="23.88671875" customWidth="1"/>
+    <col min="19" max="19" width="27.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -4335,7 +4333,7 @@
         <v>0.80694444444444446</v>
       </c>
       <c r="S2" t="s">
-        <v>168</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -4621,7 +4619,7 @@
         <v>46230.862500000003</v>
       </c>
       <c r="S16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
@@ -4653,6 +4651,7 @@
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -4770,7 +4769,7 @@
         <v>0.3923611111111111</v>
       </c>
       <c r="S2" t="s">
-        <v>166</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -5088,6 +5087,7 @@
   <cols>
     <col min="1" max="1" width="10.77734375" customWidth="1"/>
     <col min="17" max="17" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -5175,7 +5175,7 @@
         <v>0.61944444444444446</v>
       </c>
       <c r="S2" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -5493,6 +5493,7 @@
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -5610,7 +5611,7 @@
         <v>0.3263888888888889</v>
       </c>
       <c r="S2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -5928,6 +5929,7 @@
   <cols>
     <col min="1" max="1" width="11.6640625" customWidth="1"/>
     <col min="17" max="17" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="30.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -6015,7 +6017,7 @@
         <v>0.43194444444444452</v>
       </c>
       <c r="S2" t="s">
-        <v>166</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -6328,7 +6330,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:S17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6337,6 +6338,8 @@
     <col min="6" max="6" width="3.88671875" customWidth="1"/>
     <col min="8" max="8" width="4.6640625" customWidth="1"/>
     <col min="17" max="17" width="23.6640625" customWidth="1"/>
+    <col min="19" max="19" width="30.21875" customWidth="1"/>
+    <col min="20" max="20" width="23.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -6731,13 +6734,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S16" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <filterColumn colId="18">
-      <filters>
-        <filter val="under using engine"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:S17" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6750,6 +6747,7 @@
     <col min="1" max="1" width="30.88671875" customWidth="1"/>
     <col min="14" max="14" width="15.21875" customWidth="1"/>
     <col min="17" max="17" width="19.6640625" customWidth="1"/>
+    <col min="19" max="19" width="30.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -7155,6 +7153,7 @@
   <cols>
     <col min="1" max="1" width="27.21875" customWidth="1"/>
     <col min="17" max="17" width="19.77734375" customWidth="1"/>
+    <col min="19" max="19" width="37" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -7244,7 +7243,7 @@
         <v>0.9243055555555556</v>
       </c>
       <c r="S2" t="s">
-        <v>168</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -7273,7 +7272,7 @@
         <v>0.52638888888888891</v>
       </c>
       <c r="S3" t="s">
-        <v>168</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -7299,7 +7298,7 @@
         <v>46223.232638888891</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="S4" t="s">
         <v>19</v>
@@ -7371,7 +7370,7 @@
         <v>20</v>
       </c>
       <c r="S7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
@@ -7394,7 +7393,7 @@
         <v>20</v>
       </c>
       <c r="S8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
@@ -7592,6 +7591,7 @@
   <cols>
     <col min="1" max="1" width="10.33203125" customWidth="1"/>
     <col min="17" max="17" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="32.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -7679,7 +7679,7 @@
         <v>0.33055555555555549</v>
       </c>
       <c r="S2" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -7705,7 +7705,7 @@
         <v>46223</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="S3" t="s">
         <v>19</v>
@@ -7982,7 +7982,7 @@
         <v>46231.337500000001</v>
       </c>
       <c r="S17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -7996,6 +7996,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="17" max="17" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="34.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -8083,7 +8084,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="S2" t="s">
-        <v>173</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -8109,10 +8110,10 @@
         <v>46222</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="S3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -8158,7 +8159,7 @@
         <v>0.11874999999999999</v>
       </c>
       <c r="S5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
@@ -8181,7 +8182,7 @@
         <v>20</v>
       </c>
       <c r="S6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
@@ -8267,7 +8268,7 @@
         <v>46226.779861111107</v>
       </c>
       <c r="S10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
@@ -8284,7 +8285,7 @@
         <v>46227.070833333331</v>
       </c>
       <c r="S11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
@@ -8301,7 +8302,7 @@
         <v>46227.820138888892</v>
       </c>
       <c r="S12" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -8318,7 +8319,7 @@
         <v>46228.93472222222</v>
       </c>
       <c r="S13" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -8335,7 +8336,7 @@
         <v>46229.253472222219</v>
       </c>
       <c r="S14" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -8352,7 +8353,7 @@
         <v>46230.348611111112</v>
       </c>
       <c r="S15" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
@@ -8369,7 +8370,7 @@
         <v>46230.81527777778</v>
       </c>
       <c r="S16" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
@@ -8386,7 +8387,7 @@
         <v>46231.05</v>
       </c>
       <c r="S17" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -8401,6 +8402,7 @@
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.6640625" customWidth="1"/>
+    <col min="19" max="19" width="33.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -8490,7 +8492,7 @@
         <v>0.43611111111111112</v>
       </c>
       <c r="S2" t="s">
-        <v>166</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -8519,7 +8521,7 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="S3" t="s">
-        <v>168</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -8545,7 +8547,7 @@
         <v>46223</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="S4" t="s">
         <v>19</v>
@@ -8663,7 +8665,7 @@
         <v>20</v>
       </c>
       <c r="S9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
@@ -8686,7 +8688,7 @@
         <v>20</v>
       </c>
       <c r="S10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
@@ -8703,7 +8705,7 @@
         <v>46226.581944444442</v>
       </c>
       <c r="S11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
@@ -8720,7 +8722,7 @@
         <v>46226.581944444442</v>
       </c>
       <c r="S12" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -8737,7 +8739,7 @@
         <v>46226.581944444442</v>
       </c>
       <c r="S13" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -8771,7 +8773,7 @@
         <v>46228.990972222222</v>
       </c>
       <c r="S15" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
@@ -8828,6 +8830,7 @@
     <col min="7" max="11" width="8.88671875" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="21.109375" customWidth="1"/>
     <col min="17" max="17" width="21.109375" customWidth="1"/>
+    <col min="19" max="19" width="31.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -8915,7 +8918,7 @@
         <v>0.42499999999999999</v>
       </c>
       <c r="S2" t="s">
-        <v>173</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -8941,7 +8944,7 @@
         <v>46223.240277777782</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S3" t="s">
         <v>19</v>
@@ -8990,7 +8993,7 @@
         <v>0.24027777777777781</v>
       </c>
       <c r="S5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
@@ -9235,6 +9238,7 @@
     <col min="6" max="6" width="8.109375" customWidth="1"/>
     <col min="17" max="17" width="10.5546875" style="4" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.88671875" style="8" customWidth="1"/>
+    <col min="19" max="19" width="41.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -9322,7 +9326,7 @@
         <v>0.4375</v>
       </c>
       <c r="S2" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -9348,7 +9352,7 @@
         <v>46223</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="S3" t="s">
         <v>19</v>
@@ -9557,7 +9561,7 @@
         <v>46228.267361111109</v>
       </c>
       <c r="S13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">

--- a/dados/SURVEY_STARNAV.xlsx
+++ b/dados/SURVEY_STARNAV.xlsx
@@ -2727,7 +2727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="21.6640625" customWidth="1" min="17" max="17"/>
@@ -3236,9 +3236,6 @@
       <c r="A19" s="13" t="n">
         <v>46232.29444444444</v>
       </c>
-      <c r="B19" t="n">
-        <v/>
-      </c>
       <c r="M19" t="n">
         <v>-22.544794</v>
       </c>
@@ -3248,10 +3245,32 @@
       <c r="Q19" s="13" t="n">
         <v>46231.92916666667</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n">
+        <v>46234.66458333333</v>
+      </c>
+      <c r="B20" t="n">
         <v/>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="M20" t="n">
+        <v>-22.546993</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-40.068214</v>
+      </c>
+      <c r="Q20" s="13" t="n">
+        <v>46234.46458333333</v>
+      </c>
+      <c r="R20" t="n">
+        <v/>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>
@@ -3268,7 +3287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="38.21875" customWidth="1" min="1" max="1"/>
@@ -3779,9 +3798,6 @@
       <c r="A19" s="13" t="n">
         <v>46232.29444444444</v>
       </c>
-      <c r="B19" t="n">
-        <v/>
-      </c>
       <c r="M19" t="n">
         <v>-21.974453</v>
       </c>
@@ -3791,10 +3807,32 @@
       <c r="Q19" s="13" t="n">
         <v>46232.29027777778</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n">
+        <v>46234.66458333333</v>
+      </c>
+      <c r="B20" t="n">
         <v/>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="M20" t="n">
+        <v>-21.93272</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-39.784393</v>
+      </c>
+      <c r="Q20" s="13" t="n">
+        <v>46234.63611111111</v>
+      </c>
+      <c r="R20" t="n">
+        <v/>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>
@@ -3811,7 +3849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.5546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4320,9 +4358,6 @@
       <c r="A19" s="13" t="n">
         <v>46232.29236111111</v>
       </c>
-      <c r="B19" t="n">
-        <v/>
-      </c>
       <c r="M19" t="n">
         <v>-22.856777</v>
       </c>
@@ -4332,10 +4367,32 @@
       <c r="Q19" s="13" t="n">
         <v>46232.2875</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n">
+        <v>46234.66736111111</v>
+      </c>
+      <c r="B20" t="n">
         <v/>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="M20" t="n">
+        <v>-22.858196</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-43.162621</v>
+      </c>
+      <c r="Q20" s="13" t="n">
+        <v>46234.66458333333</v>
+      </c>
+      <c r="R20" t="n">
+        <v/>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>At Anchor</t>
         </is>
@@ -4352,7 +4409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="23.88671875" customWidth="1" min="1" max="1"/>
@@ -4913,9 +4970,6 @@
       <c r="A19" s="13" t="n">
         <v>46232.29236111111</v>
       </c>
-      <c r="B19" t="n">
-        <v/>
-      </c>
       <c r="M19" t="n">
         <v>-21.863337</v>
       </c>
@@ -4925,10 +4979,32 @@
       <c r="Q19" s="13" t="n">
         <v>46232.28958333333</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n">
+        <v>46234.66736111111</v>
+      </c>
+      <c r="B20" t="n">
         <v/>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="M20" t="n">
+        <v>-21.863316</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-41.017258</v>
+      </c>
+      <c r="Q20" s="13" t="n">
+        <v>46234.66527777778</v>
+      </c>
+      <c r="R20" t="n">
+        <v/>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>Moored</t>
         </is>
@@ -4946,7 +5022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.88671875" customWidth="1" min="1" max="1"/>
@@ -5455,9 +5531,6 @@
       <c r="A19" s="13" t="n">
         <v>46232.29236111111</v>
       </c>
-      <c r="B19" t="n">
-        <v/>
-      </c>
       <c r="M19" t="n">
         <v>-25.670572</v>
       </c>
@@ -5467,10 +5540,32 @@
       <c r="Q19" s="13" t="n">
         <v>46232.28888888889</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n">
+        <v>46234.66736111111</v>
+      </c>
+      <c r="B20" t="n">
         <v/>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="M20" t="n">
+        <v>-25.79954</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-43.263905</v>
+      </c>
+      <c r="Q20" s="13" t="n">
+        <v>46234.50208333333</v>
+      </c>
+      <c r="R20" t="n">
+        <v/>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>
@@ -5487,7 +5582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.5546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6045,9 +6140,6 @@
       <c r="A19" s="13" t="n">
         <v>46232.29236111111</v>
       </c>
-      <c r="B19" t="n">
-        <v/>
-      </c>
       <c r="M19" t="n">
         <v>-22.86096</v>
       </c>
@@ -6057,10 +6149,32 @@
       <c r="Q19" s="13" t="n">
         <v>46232.28888888889</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n">
+        <v>46234.66736111111</v>
+      </c>
+      <c r="B20" t="n">
         <v/>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="M20" t="n">
+        <v>-22.861601</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-43.175812</v>
+      </c>
+      <c r="Q20" s="13" t="n">
+        <v>46234.66527777778</v>
+      </c>
+      <c r="R20" t="n">
+        <v/>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>At Anchor</t>
         </is>
@@ -6077,7 +6191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.77734375" customWidth="1" min="1" max="1"/>
@@ -6585,9 +6699,6 @@
       <c r="A19" s="13" t="n">
         <v>46232.29236111111</v>
       </c>
-      <c r="B19" t="n">
-        <v/>
-      </c>
       <c r="M19" t="n">
         <v>-22.853029</v>
       </c>
@@ -6597,12 +6708,34 @@
       <c r="Q19" s="13" t="n">
         <v>46232.28958333333</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n">
+        <v>46234.66736111111</v>
+      </c>
+      <c r="B20" t="n">
         <v/>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Stopped</t>
+      <c r="M20" t="n">
+        <v>-22.856613</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-43.16613</v>
+      </c>
+      <c r="Q20" s="13" t="n">
+        <v>46234.66597222222</v>
+      </c>
+      <c r="R20" t="n">
+        <v/>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Moored</t>
         </is>
       </c>
     </row>
@@ -6617,7 +6750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.5546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7175,9 +7308,6 @@
       <c r="A19" s="13" t="n">
         <v>46232.29236111111</v>
       </c>
-      <c r="B19" t="n">
-        <v/>
-      </c>
       <c r="M19" t="n">
         <v>-26.856745</v>
       </c>
@@ -7187,10 +7317,32 @@
       <c r="Q19" s="13" t="n">
         <v>46120.32569444444</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n">
+        <v>46234.66736111111</v>
+      </c>
+      <c r="B20" t="n">
         <v/>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="M20" t="n">
+        <v>-26.856745</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-48.721401</v>
+      </c>
+      <c r="Q20" s="13" t="n">
+        <v>46120.32569444444</v>
+      </c>
+      <c r="R20" t="n">
+        <v/>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>
@@ -7207,7 +7359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="24.6640625" customWidth="1" min="1" max="1"/>
@@ -7716,9 +7868,6 @@
       <c r="A19" s="13" t="n">
         <v>46232.29236111111</v>
       </c>
-      <c r="B19" t="n">
-        <v/>
-      </c>
       <c r="M19" t="n">
         <v>-24.594416</v>
       </c>
@@ -7728,10 +7877,32 @@
       <c r="Q19" s="13" t="n">
         <v>46232.26875</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n">
+        <v>46234.66736111111</v>
+      </c>
+      <c r="B20" t="n">
         <v/>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="M20" t="n">
+        <v>-23.373629</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-42.836628</v>
+      </c>
+      <c r="Q20" s="13" t="n">
+        <v>46233.89305555556</v>
+      </c>
+      <c r="R20" t="n">
+        <v/>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -7748,7 +7919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="24.77734375" customWidth="1" min="1" max="1"/>
@@ -8260,9 +8431,6 @@
       <c r="A19" s="13" t="n">
         <v>46232.29444444444</v>
       </c>
-      <c r="B19" t="n">
-        <v/>
-      </c>
       <c r="M19" t="n">
         <v>-24.037725</v>
       </c>
@@ -8272,10 +8440,32 @@
       <c r="Q19" s="13" t="n">
         <v>46232.29236111111</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n">
+        <v>46234.66458333333</v>
+      </c>
+      <c r="B20" t="n">
         <v/>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="M20" t="n">
+        <v>-24.609463</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-42.614685</v>
+      </c>
+      <c r="Q20" s="13" t="n">
+        <v>46232.76041666666</v>
+      </c>
+      <c r="R20" t="n">
+        <v/>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -8293,7 +8483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.88671875" customWidth="1" min="1" max="1"/>
@@ -8804,9 +8994,6 @@
       <c r="A19" s="13" t="n">
         <v>46232.29444444444</v>
       </c>
-      <c r="B19" t="n">
-        <v/>
-      </c>
       <c r="M19" t="n">
         <v>-24.703707</v>
       </c>
@@ -8816,12 +9003,34 @@
       <c r="Q19" s="13" t="n">
         <v>46232.28958333333</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n">
+        <v>46234.66458333333</v>
+      </c>
+      <c r="B20" t="n">
         <v/>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Stopped</t>
+      <c r="M20" t="n">
+        <v>-24.703972</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-42.382092</v>
+      </c>
+      <c r="Q20" s="13" t="n">
+        <v>46232.58888888889</v>
+      </c>
+      <c r="R20" t="n">
+        <v/>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
         </is>
       </c>
     </row>
@@ -8836,7 +9045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="27.21875" customWidth="1" min="1" max="1"/>
@@ -9379,9 +9588,6 @@
       <c r="A20" s="13" t="n">
         <v>46232.29444444444</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-22.427124</v>
       </c>
@@ -9391,10 +9597,32 @@
       <c r="Q20" s="13" t="n">
         <v>46232.27638888889</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n">
+        <v>46234.66458333333</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="M21" t="n">
+        <v>-22.533188</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-40.152752</v>
+      </c>
+      <c r="Q21" s="13" t="n">
+        <v>46234.47847222222</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -9412,7 +9640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" customWidth="1" min="1" max="1"/>
@@ -9922,9 +10150,6 @@
       <c r="A19" s="13" t="n">
         <v>46232.29444444444</v>
       </c>
-      <c r="B19" t="n">
-        <v/>
-      </c>
       <c r="M19" t="n">
         <v>-22.893719</v>
       </c>
@@ -9934,12 +10159,34 @@
       <c r="Q19" s="13" t="n">
         <v>46232.29027777778</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n">
+        <v>46234.66458333333</v>
+      </c>
+      <c r="B20" t="n">
         <v/>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Stopped</t>
+      <c r="M20" t="n">
+        <v>-23.387266</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-42.956207</v>
+      </c>
+      <c r="Q20" s="13" t="n">
+        <v>46233.78402777778</v>
+      </c>
+      <c r="R20" t="n">
+        <v/>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
         </is>
       </c>
     </row>
@@ -9954,7 +10201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.5546875" bestFit="1" customWidth="1" min="17" max="17"/>
@@ -10463,9 +10710,6 @@
       <c r="A19" s="13" t="n">
         <v>46232.29444444444</v>
       </c>
-      <c r="B19" t="n">
-        <v/>
-      </c>
       <c r="M19" t="n">
         <v>-21.856209</v>
       </c>
@@ -10475,12 +10719,34 @@
       <c r="Q19" s="13" t="n">
         <v>46232.29166666666</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n">
+        <v>46234.66458333333</v>
+      </c>
+      <c r="B20" t="n">
         <v/>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>At Anchor</t>
+      <c r="M20" t="n">
+        <v>-22.43685</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-40.42503</v>
+      </c>
+      <c r="Q20" s="13" t="n">
+        <v>46233.72152777778</v>
+      </c>
+      <c r="R20" t="n">
+        <v/>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Stopped</t>
         </is>
       </c>
     </row>
@@ -10495,7 +10761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.5546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11023,9 +11289,6 @@
       <c r="A20" s="13" t="n">
         <v>46232.29444444444</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-21.855047</v>
       </c>
@@ -11035,12 +11298,34 @@
       <c r="Q20" s="13" t="n">
         <v>46232.28888888889</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n">
+        <v>46234.66458333333</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Moored</t>
+      <c r="M21" t="n">
+        <v>-22.822378</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-43.13422</v>
+      </c>
+      <c r="Q21" s="13" t="n">
+        <v>46234.66111111111</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
         </is>
       </c>
     </row>
@@ -11055,7 +11340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="27.5546875" customWidth="1" min="1" max="1"/>
@@ -11569,9 +11854,6 @@
       <c r="A19" s="13" t="n">
         <v>46232.29444444444</v>
       </c>
-      <c r="B19" t="n">
-        <v/>
-      </c>
       <c r="M19" t="n">
         <v>-21.865593</v>
       </c>
@@ -11581,12 +11863,34 @@
       <c r="Q19" s="13" t="n">
         <v>46232.28888888889</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n">
+        <v>46234.66458333333</v>
+      </c>
+      <c r="B20" t="n">
         <v/>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>At Anchor</t>
+      <c r="M20" t="n">
+        <v>-21.976345</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-39.835575</v>
+      </c>
+      <c r="Q20" s="13" t="n">
+        <v>46234.63611111111</v>
+      </c>
+      <c r="R20" t="n">
+        <v/>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Stopped</t>
         </is>
       </c>
     </row>
@@ -11601,7 +11905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.5546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -12113,9 +12417,6 @@
       <c r="A19" s="13" t="n">
         <v>46232.29444444444</v>
       </c>
-      <c r="B19" t="n">
-        <v/>
-      </c>
       <c r="M19" t="n">
         <v>-22.722918</v>
       </c>
@@ -12125,12 +12426,34 @@
       <c r="Q19" s="13" t="n">
         <v>46232.28263888889</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n">
+        <v>46234.66458333333</v>
+      </c>
+      <c r="B20" t="n">
         <v/>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Stopped</t>
+      <c r="M20" t="n">
+        <v>-22.68343</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-40.551006</v>
+      </c>
+      <c r="Q20" s="13" t="n">
+        <v>46232.83888888889</v>
+      </c>
+      <c r="R20" t="n">
+        <v/>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
         </is>
       </c>
     </row>

--- a/dados/SURVEY_STARNAV.xlsx
+++ b/dados/SURVEY_STARNAV.xlsx
@@ -2727,7 +2727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="21.6640625" customWidth="1" min="17" max="17"/>
@@ -3255,9 +3255,6 @@
       <c r="A20" s="13" t="n">
         <v>46234.66458333333</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-22.546993</v>
       </c>
@@ -3267,10 +3264,32 @@
       <c r="Q20" s="13" t="n">
         <v>46234.46458333333</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="M21" t="n">
+        <v>-22.396486</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-40.109241</v>
+      </c>
+      <c r="Q21" s="13" t="n">
+        <v>46235.30625</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>
@@ -3287,7 +3306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="38.21875" customWidth="1" min="1" max="1"/>
@@ -3817,9 +3836,6 @@
       <c r="A20" s="13" t="n">
         <v>46234.66458333333</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-21.93272</v>
       </c>
@@ -3829,10 +3845,32 @@
       <c r="Q20" s="13" t="n">
         <v>46234.63611111111</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="M21" t="n">
+        <v>-21.93272</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-39.784393</v>
+      </c>
+      <c r="Q21" s="13" t="n">
+        <v>46234.63611111111</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>
@@ -3849,7 +3887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.5546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4377,9 +4415,6 @@
       <c r="A20" s="13" t="n">
         <v>46234.66736111111</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-22.858196</v>
       </c>
@@ -4389,10 +4424,32 @@
       <c r="Q20" s="13" t="n">
         <v>46234.66458333333</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n">
+        <v>46235.40069444444</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="M21" t="n">
+        <v>-22.859173</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-43.162827</v>
+      </c>
+      <c r="Q21" s="13" t="n">
+        <v>46235.39583333334</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>At Anchor</t>
         </is>
@@ -4409,7 +4466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="23.88671875" customWidth="1" min="1" max="1"/>
@@ -4989,9 +5046,6 @@
       <c r="A20" s="13" t="n">
         <v>46234.66736111111</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-21.863316</v>
       </c>
@@ -5001,12 +5055,34 @@
       <c r="Q20" s="13" t="n">
         <v>46234.66527777778</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n">
+        <v>46235.40069444444</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Moored</t>
+      <c r="M21" t="n">
+        <v>-21.991858</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-40.75536</v>
+      </c>
+      <c r="Q21" s="13" t="n">
+        <v>46235.06805555556</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.88671875" customWidth="1" min="1" max="1"/>
@@ -5550,9 +5626,6 @@
       <c r="A20" s="13" t="n">
         <v>46234.66736111111</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-25.79954</v>
       </c>
@@ -5562,12 +5635,34 @@
       <c r="Q20" s="13" t="n">
         <v>46234.50208333333</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n">
+        <v>46235.40069444444</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Stopped</t>
+      <c r="M21" t="n">
+        <v>-23.638178</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-43.141171</v>
+      </c>
+      <c r="Q21" s="13" t="n">
+        <v>46235.39236111111</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.5546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6159,9 +6254,6 @@
       <c r="A20" s="13" t="n">
         <v>46234.66736111111</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-22.861601</v>
       </c>
@@ -6171,10 +6263,32 @@
       <c r="Q20" s="13" t="n">
         <v>46234.66527777778</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n">
+        <v>46235.40069444444</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="M21" t="n">
+        <v>-22.862339</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-43.175774</v>
+      </c>
+      <c r="Q21" s="13" t="n">
+        <v>46235.39722222222</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>At Anchor</t>
         </is>
@@ -6191,7 +6305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.77734375" customWidth="1" min="1" max="1"/>
@@ -6718,9 +6832,6 @@
       <c r="A20" s="13" t="n">
         <v>46234.66736111111</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-22.856613</v>
       </c>
@@ -6730,12 +6841,34 @@
       <c r="Q20" s="13" t="n">
         <v>46234.66597222222</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n">
+        <v>46235.40069444444</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Moored</t>
+      <c r="M21" t="n">
+        <v>-22.857548</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-43.166058</v>
+      </c>
+      <c r="Q21" s="13" t="n">
+        <v>46235.39583333334</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
         </is>
       </c>
     </row>
@@ -6750,7 +6883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.5546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7327,9 +7460,6 @@
       <c r="A20" s="13" t="n">
         <v>46234.66736111111</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-26.856745</v>
       </c>
@@ -7339,10 +7469,32 @@
       <c r="Q20" s="13" t="n">
         <v>46120.32569444444</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n">
+        <v>46235.40069444444</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="M21" t="n">
+        <v>-26.856745</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-48.721401</v>
+      </c>
+      <c r="Q21" s="13" t="n">
+        <v>46120.32569444444</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>
@@ -7359,7 +7511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="24.6640625" customWidth="1" min="1" max="1"/>
@@ -7887,9 +8039,6 @@
       <c r="A20" s="13" t="n">
         <v>46234.66736111111</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-23.373629</v>
       </c>
@@ -7899,10 +8048,32 @@
       <c r="Q20" s="13" t="n">
         <v>46233.89305555556</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n">
+        <v>46235.40069444444</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="M21" t="n">
+        <v>-23.373629</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-42.836628</v>
+      </c>
+      <c r="Q21" s="13" t="n">
+        <v>46233.89305555556</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -7919,7 +8090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="24.77734375" customWidth="1" min="1" max="1"/>
@@ -8450,9 +8621,6 @@
       <c r="A20" s="13" t="n">
         <v>46234.66458333333</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-24.609463</v>
       </c>
@@ -8462,12 +8630,34 @@
       <c r="Q20" s="13" t="n">
         <v>46232.76041666666</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Underway using Engine</t>
+      <c r="M21" t="n">
+        <v>-22.855375</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-43.144661</v>
+      </c>
+      <c r="Q21" s="13" t="n">
+        <v>46235.4</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
         </is>
       </c>
     </row>
@@ -8483,7 +8673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.88671875" customWidth="1" min="1" max="1"/>
@@ -9013,9 +9203,6 @@
       <c r="A20" s="13" t="n">
         <v>46234.66458333333</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-24.703972</v>
       </c>
@@ -9025,10 +9212,32 @@
       <c r="Q20" s="13" t="n">
         <v>46232.58888888889</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="M21" t="n">
+        <v>-23.896917</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-42.725639</v>
+      </c>
+      <c r="Q21" s="13" t="n">
+        <v>46235.38888888889</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -9045,7 +9254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="27.21875" customWidth="1" min="1" max="1"/>
@@ -9607,9 +9816,6 @@
       <c r="A21" s="13" t="n">
         <v>46234.66458333333</v>
       </c>
-      <c r="B21" t="n">
-        <v/>
-      </c>
       <c r="M21" t="n">
         <v>-22.533188</v>
       </c>
@@ -9619,12 +9825,34 @@
       <c r="Q21" s="13" t="n">
         <v>46234.47847222222</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Underway using Engine</t>
+      <c r="M22" t="n">
+        <v>-21.863905</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-41.016941</v>
+      </c>
+      <c r="Q22" s="13" t="n">
+        <v>46235.40069444444</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Moored</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" customWidth="1" min="1" max="1"/>
@@ -10169,9 +10397,6 @@
       <c r="A20" s="13" t="n">
         <v>46234.66458333333</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-23.387266</v>
       </c>
@@ -10181,10 +10406,32 @@
       <c r="Q20" s="13" t="n">
         <v>46233.78402777778</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="M21" t="n">
+        <v>-23.387266</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-42.956207</v>
+      </c>
+      <c r="Q21" s="13" t="n">
+        <v>46233.78402777778</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -10201,7 +10448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.5546875" bestFit="1" customWidth="1" min="17" max="17"/>
@@ -10729,9 +10976,6 @@
       <c r="A20" s="13" t="n">
         <v>46234.66458333333</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-22.43685</v>
       </c>
@@ -10741,12 +10985,34 @@
       <c r="Q20" s="13" t="n">
         <v>46233.72152777778</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Stopped</t>
+      <c r="M21" t="n">
+        <v>-22.451303</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-40.411659</v>
+      </c>
+      <c r="Q21" s="13" t="n">
+        <v>46235.11736111111</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
         </is>
       </c>
     </row>
@@ -10761,7 +11027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.5546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -11308,9 +11574,6 @@
       <c r="A21" s="13" t="n">
         <v>46234.66458333333</v>
       </c>
-      <c r="B21" t="n">
-        <v/>
-      </c>
       <c r="M21" t="n">
         <v>-22.822378</v>
       </c>
@@ -11320,12 +11583,34 @@
       <c r="Q21" s="13" t="n">
         <v>46234.66111111111</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Restricted Manoeuvrability</t>
+      <c r="M22" t="n">
+        <v>-23.084103</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-42.557159</v>
+      </c>
+      <c r="Q22" s="13" t="n">
+        <v>46235.40138888889</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
         </is>
       </c>
     </row>
@@ -11340,7 +11625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="27.5546875" customWidth="1" min="1" max="1"/>
@@ -11873,9 +12158,6 @@
       <c r="A20" s="13" t="n">
         <v>46234.66458333333</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-21.976345</v>
       </c>
@@ -11885,10 +12167,32 @@
       <c r="Q20" s="13" t="n">
         <v>46234.63611111111</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="M21" t="n">
+        <v>-21.96414</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-39.826088</v>
+      </c>
+      <c r="Q21" s="13" t="n">
+        <v>46235.36944444444</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>
@@ -11905,7 +12209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.5546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -12436,9 +12740,6 @@
       <c r="A20" s="13" t="n">
         <v>46234.66458333333</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-22.68343</v>
       </c>
@@ -12448,12 +12749,34 @@
       <c r="Q20" s="13" t="n">
         <v>46232.83888888889</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Underway using Engine</t>
+      <c r="M21" t="n">
+        <v>-21.862419</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-41.017845</v>
+      </c>
+      <c r="Q21" s="13" t="n">
+        <v>46235.40208333333</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Stopped</t>
         </is>
       </c>
     </row>

--- a/dados/SURVEY_STARNAV.xlsx
+++ b/dados/SURVEY_STARNAV.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.7109375" customWidth="1" min="1" max="1"/>
@@ -1027,9 +1027,6 @@
       <c r="A22" s="10" t="n">
         <v>46236.36527777778</v>
       </c>
-      <c r="B22" t="n">
-        <v/>
-      </c>
       <c r="M22" t="n">
         <v>-22.855698</v>
       </c>
@@ -1039,12 +1036,34 @@
       <c r="Q22" s="10" t="n">
         <v>46236.36111111111</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" t="n">
         <v/>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>Stopped</t>
+      <c r="M23" t="n">
+        <v>-22.854778</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-43.144005</v>
+      </c>
+      <c r="Q23" s="10" t="n">
+        <v>46237.32152777778</v>
+      </c>
+      <c r="R23" t="n">
+        <v/>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38.28515625" customWidth="1" min="1" max="1"/>
@@ -1628,9 +1647,6 @@
       <c r="A22" s="10" t="n">
         <v>46236.36527777778</v>
       </c>
-      <c r="B22" t="n">
-        <v/>
-      </c>
       <c r="M22" t="n">
         <v>-21.935139</v>
       </c>
@@ -1640,10 +1656,32 @@
       <c r="Q22" s="10" t="n">
         <v>46236.34930555556</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" t="n">
         <v/>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="M23" t="n">
+        <v>-21.962212</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-39.924904</v>
+      </c>
+      <c r="Q23" s="10" t="n">
+        <v>46237.30833333333</v>
+      </c>
+      <c r="R23" t="n">
+        <v/>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -1660,7 +1698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2226,9 +2264,6 @@
       <c r="A22" s="10" t="n">
         <v>46236.36319444444</v>
       </c>
-      <c r="B22" t="n">
-        <v/>
-      </c>
       <c r="M22" t="n">
         <v>-22.859055</v>
       </c>
@@ -2238,12 +2273,34 @@
       <c r="Q22" s="10" t="n">
         <v>46236.36111111111</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" t="n">
         <v/>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>At Anchor</t>
+      <c r="M23" t="n">
+        <v>-22.887428</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-43.215561</v>
+      </c>
+      <c r="Q23" s="10" t="n">
+        <v>46237.32152777778</v>
+      </c>
+      <c r="R23" t="n">
+        <v/>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23.85546875" customWidth="1" min="1" max="1"/>
@@ -2876,9 +2933,6 @@
       <c r="A22" s="10" t="n">
         <v>46236.36319444444</v>
       </c>
-      <c r="B22" t="n">
-        <v/>
-      </c>
       <c r="M22" t="n">
         <v>-23.370502</v>
       </c>
@@ -2888,10 +2942,32 @@
       <c r="Q22" s="10" t="n">
         <v>46236.03472222222</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" t="n">
         <v/>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="M23" t="n">
+        <v>-23.333735</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-40.133389</v>
+      </c>
+      <c r="Q23" s="10" t="n">
+        <v>46237.30902777778</v>
+      </c>
+      <c r="R23" t="n">
+        <v/>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -2909,7 +2985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.85546875" customWidth="1" min="1" max="1"/>
@@ -3475,9 +3551,6 @@
       <c r="A22" s="10" t="n">
         <v>46236.36319444444</v>
       </c>
-      <c r="B22" t="n">
-        <v/>
-      </c>
       <c r="M22" t="n">
         <v>-22.839684</v>
       </c>
@@ -3487,10 +3560,32 @@
       <c r="Q22" s="10" t="n">
         <v>46236.36111111111</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" t="n">
         <v/>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="M23" t="n">
+        <v>-22.838448</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-43.141331</v>
+      </c>
+      <c r="Q23" s="10" t="n">
+        <v>46237.32152777778</v>
+      </c>
+      <c r="R23" t="n">
+        <v/>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>
@@ -3507,7 +3602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4122,9 +4217,6 @@
       <c r="A22" s="10" t="n">
         <v>46236.36319444444</v>
       </c>
-      <c r="B22" t="n">
-        <v/>
-      </c>
       <c r="M22" t="n">
         <v>-22.862318</v>
       </c>
@@ -4134,10 +4226,32 @@
       <c r="Q22" s="10" t="n">
         <v>46236.36180555556</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" t="n">
         <v/>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="M23" t="n">
+        <v>-22.86203</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-43.175774</v>
+      </c>
+      <c r="Q23" s="10" t="n">
+        <v>46237.32222222222</v>
+      </c>
+      <c r="R23" t="n">
+        <v/>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>At Anchor</t>
         </is>
@@ -4154,7 +4268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" customWidth="1" min="1" max="1"/>
@@ -4719,9 +4833,6 @@
       <c r="A22" s="10" t="n">
         <v>46236.36319444444</v>
       </c>
-      <c r="B22" t="n">
-        <v/>
-      </c>
       <c r="M22" t="n">
         <v>-22.857607</v>
       </c>
@@ -4731,10 +4842,32 @@
       <c r="Q22" s="10" t="n">
         <v>46236.36180555556</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" t="n">
         <v/>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="M23" t="n">
+        <v>-22.857306</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-43.165932</v>
+      </c>
+      <c r="Q23" s="10" t="n">
+        <v>46237.32222222222</v>
+      </c>
+      <c r="R23" t="n">
+        <v/>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>At Anchor</t>
         </is>
@@ -4751,7 +4884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5366,9 +5499,6 @@
       <c r="A22" s="10" t="n">
         <v>46236.36319444444</v>
       </c>
-      <c r="B22" t="n">
-        <v/>
-      </c>
       <c r="M22" t="n">
         <v>-26.856745</v>
       </c>
@@ -5378,10 +5508,32 @@
       <c r="Q22" s="10" t="n">
         <v>46120.32569444444</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" t="n">
         <v/>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="M23" t="n">
+        <v>-26.856745</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-48.721401</v>
+      </c>
+      <c r="Q23" s="10" t="n">
+        <v>46120.32569444444</v>
+      </c>
+      <c r="R23" t="n">
+        <v/>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>
@@ -5398,7 +5550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.7109375" customWidth="1" min="1" max="1"/>
@@ -5964,9 +6116,6 @@
       <c r="A22" s="10" t="n">
         <v>46236.36319444444</v>
       </c>
-      <c r="B22" t="n">
-        <v/>
-      </c>
       <c r="M22" t="n">
         <v>-22.892349</v>
       </c>
@@ -5976,10 +6125,32 @@
       <c r="Q22" s="10" t="n">
         <v>46236.36180555556</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" t="n">
         <v/>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="M23" t="n">
+        <v>-22.838087</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-43.144295</v>
+      </c>
+      <c r="Q23" s="10" t="n">
+        <v>46237.31875</v>
+      </c>
+      <c r="R23" t="n">
+        <v/>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>
@@ -5996,7 +6167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.85546875" customWidth="1" min="1" max="1"/>
@@ -6564,9 +6735,6 @@
       <c r="A22" s="10" t="n">
         <v>46236.36527777778</v>
       </c>
-      <c r="B22" t="n">
-        <v/>
-      </c>
       <c r="M22" t="n">
         <v>-22.850817</v>
       </c>
@@ -6576,12 +6744,34 @@
       <c r="Q22" s="10" t="n">
         <v>46236.36111111111</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" t="n">
         <v/>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>At Anchor</t>
+      <c r="M23" t="n">
+        <v>-22.895683</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-43.205006</v>
+      </c>
+      <c r="Q23" s="10" t="n">
+        <v>46237.31666666667</v>
+      </c>
+      <c r="R23" t="n">
+        <v/>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Stopped</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.28515625" customWidth="1" min="1" max="1"/>
@@ -7196,9 +7386,6 @@
       <c r="A23" s="10" t="n">
         <v>46236.36527777778</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-22.180353</v>
       </c>
@@ -7208,12 +7395,34 @@
       <c r="Q23" s="10" t="n">
         <v>46236.13194444445</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B24" t="n">
         <v/>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Underway using Engine</t>
+      <c r="M24" t="n">
+        <v>-22.464121</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-40.058056</v>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <v>46237.31736111111</v>
+      </c>
+      <c r="R24" t="n">
+        <v/>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Stopped</t>
         </is>
       </c>
     </row>
@@ -7229,7 +7438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -7796,9 +8005,6 @@
       <c r="A22" s="10" t="n">
         <v>46236.36527777778</v>
       </c>
-      <c r="B22" t="n">
-        <v/>
-      </c>
       <c r="M22" t="n">
         <v>-23.387266</v>
       </c>
@@ -7808,10 +8014,32 @@
       <c r="Q22" s="10" t="n">
         <v>46233.78402777778</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" t="n">
         <v/>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="M23" t="n">
+        <v>-24.568388</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-42.473843</v>
+      </c>
+      <c r="Q23" s="10" t="n">
+        <v>46236.91458333333</v>
+      </c>
+      <c r="R23" t="n">
+        <v/>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -7828,7 +8056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" bestFit="1" customWidth="1" min="17" max="17"/>
@@ -8394,9 +8622,6 @@
       <c r="A22" s="10" t="n">
         <v>46236.36527777778</v>
       </c>
-      <c r="B22" t="n">
-        <v/>
-      </c>
       <c r="M22" t="n">
         <v>-22.395788</v>
       </c>
@@ -8406,10 +8631,32 @@
       <c r="Q22" s="10" t="n">
         <v>46236.03541666667</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" t="n">
         <v/>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="M23" t="n">
+        <v>-22.445057</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-40.420341</v>
+      </c>
+      <c r="Q23" s="10" t="n">
+        <v>46237.32430555556</v>
+      </c>
+      <c r="R23" t="n">
+        <v/>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>Restricted Manoeuvrability</t>
         </is>
@@ -8426,7 +8673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9011,9 +9258,6 @@
       <c r="A23" s="10" t="n">
         <v>46236.36527777778</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-21.855019</v>
       </c>
@@ -9023,10 +9267,32 @@
       <c r="Q23" s="10" t="n">
         <v>46236.35833333333</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B24" t="n">
         <v/>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="M24" t="n">
+        <v>-21.855021</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-41.008717</v>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <v>46237.32569444444</v>
+      </c>
+      <c r="R24" t="n">
+        <v/>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>Moored</t>
         </is>
@@ -9043,7 +9309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.5703125" customWidth="1" min="1" max="1"/>
@@ -9614,9 +9880,6 @@
       <c r="A22" s="10" t="n">
         <v>46236.36527777778</v>
       </c>
-      <c r="B22" t="n">
-        <v/>
-      </c>
       <c r="M22" t="n">
         <v>-22.164833</v>
       </c>
@@ -9626,10 +9889,32 @@
       <c r="Q22" s="10" t="n">
         <v>46236.34652777778</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" t="n">
         <v/>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="M23" t="n">
+        <v>-22.197227</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-40.792225</v>
+      </c>
+      <c r="Q23" s="10" t="n">
+        <v>46237.32430555556</v>
+      </c>
+      <c r="R23" t="n">
+        <v/>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -9646,7 +9931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10215,9 +10500,6 @@
       <c r="A22" s="10" t="n">
         <v>46236.36527777778</v>
       </c>
-      <c r="B22" t="n">
-        <v/>
-      </c>
       <c r="M22" t="n">
         <v>-21.882368</v>
       </c>
@@ -10227,12 +10509,34 @@
       <c r="Q22" s="10" t="n">
         <v>46236.28611111111</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" t="n">
         <v/>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>Underway using Engine</t>
+      <c r="M23" t="n">
+        <v>-22.710012</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-40.691872</v>
+      </c>
+      <c r="Q23" s="10" t="n">
+        <v>46237.31944444445</v>
+      </c>
+      <c r="R23" t="n">
+        <v/>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Stopped</t>
         </is>
       </c>
     </row>
@@ -10247,7 +10551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.7109375" customWidth="1" min="17" max="17"/>
@@ -10813,9 +11117,6 @@
       <c r="A22" s="10" t="n">
         <v>46236.36527777778</v>
       </c>
-      <c r="B22" t="n">
-        <v/>
-      </c>
       <c r="M22" t="n">
         <v>-22.395971</v>
       </c>
@@ -10825,10 +11126,32 @@
       <c r="Q22" s="10" t="n">
         <v>46235.70972222222</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" t="n">
         <v/>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="M23" t="n">
+        <v>-22.634569</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-39.993328</v>
+      </c>
+      <c r="Q23" s="10" t="n">
+        <v>46236.53194444445</v>
+      </c>
+      <c r="R23" t="n">
+        <v/>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>
